--- a/src/main/resources/2012/06/Papierz_Roman.xlsx
+++ b/src/main/resources/2012/06/Papierz_Roman.xlsx
@@ -8,8 +8,8 @@
     <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
   </bookViews>
   <sheets>
-    <sheet name="Projekt1" sheetId="1" state="visible" r:id="rId3"/>
-    <sheet name="Projekt2" sheetId="2" state="visible" r:id="rId4"/>
+    <sheet name="Projekt1" sheetId="1" state="visible" r:id="rId2"/>
+    <sheet name="Projekt2" sheetId="2" state="visible" r:id="rId3"/>
   </sheets>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.001"/>
   <extLst>
@@ -188,119 +188,13 @@
 </styleSheet>
 </file>
 
-<file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Office Theme">
-  <a:themeElements>
-    <a:clrScheme name="LibreOffice">
-      <a:dk1>
-        <a:srgbClr val="000000"/>
-      </a:dk1>
-      <a:lt1>
-        <a:srgbClr val="ffffff"/>
-      </a:lt1>
-      <a:dk2>
-        <a:srgbClr val="000000"/>
-      </a:dk2>
-      <a:lt2>
-        <a:srgbClr val="ffffff"/>
-      </a:lt2>
-      <a:accent1>
-        <a:srgbClr val="18a303"/>
-      </a:accent1>
-      <a:accent2>
-        <a:srgbClr val="0369a3"/>
-      </a:accent2>
-      <a:accent3>
-        <a:srgbClr val="a33e03"/>
-      </a:accent3>
-      <a:accent4>
-        <a:srgbClr val="8e03a3"/>
-      </a:accent4>
-      <a:accent5>
-        <a:srgbClr val="c99c00"/>
-      </a:accent5>
-      <a:accent6>
-        <a:srgbClr val="c9211e"/>
-      </a:accent6>
-      <a:hlink>
-        <a:srgbClr val="0000ee"/>
-      </a:hlink>
-      <a:folHlink>
-        <a:srgbClr val="551a8b"/>
-      </a:folHlink>
-    </a:clrScheme>
-    <a:fontScheme name="Office">
-      <a:majorFont>
-        <a:latin typeface="Arial" pitchFamily="0" charset="1"/>
-        <a:ea typeface="DejaVu Sans" pitchFamily="0" charset="1"/>
-        <a:cs typeface="DejaVu Sans" pitchFamily="0" charset="1"/>
-      </a:majorFont>
-      <a:minorFont>
-        <a:latin typeface="Arial" pitchFamily="0" charset="1"/>
-        <a:ea typeface="DejaVu Sans" pitchFamily="0" charset="1"/>
-        <a:cs typeface="DejaVu Sans" pitchFamily="0" charset="1"/>
-      </a:minorFont>
-    </a:fontScheme>
-    <a:fmtScheme>
-      <a:fillStyleLst>
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-      </a:fillStyleLst>
-      <a:lnStyleLst>
-        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
-          <a:prstDash val="solid"/>
-          <a:miter/>
-        </a:ln>
-        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
-          <a:prstDash val="solid"/>
-          <a:miter/>
-        </a:ln>
-        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
-          <a:prstDash val="solid"/>
-          <a:miter/>
-        </a:ln>
-      </a:lnStyleLst>
-      <a:effectStyleLst>
-        <a:effectStyle>
-          <a:effectLst/>
-        </a:effectStyle>
-        <a:effectStyle>
-          <a:effectLst/>
-        </a:effectStyle>
-        <a:effectStyle>
-          <a:effectLst/>
-        </a:effectStyle>
-      </a:effectStyleLst>
-      <a:bgFillStyleLst>
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-      </a:bgFillStyleLst>
-    </a:fmtScheme>
-  </a:themeElements>
-</a:theme>
-</file>
-
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:C1048576"/>
-  <sheetFormatPr defaultColWidth="9.13671875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="9.1484375" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="11.85"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="60.85"/>
@@ -391,12 +285,12 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:C6"/>
-  <sheetFormatPr defaultColWidth="9.13671875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="9.1484375" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="11.85"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="60.85"/>

--- a/src/main/resources/2012/06/Papierz_Roman.xlsx
+++ b/src/main/resources/2012/06/Papierz_Roman.xlsx
@@ -5,7 +5,7 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Projekt1" sheetId="1" state="visible" r:id="rId3"/>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="17">
   <si>
     <t xml:space="preserve">Data</t>
   </si>
@@ -38,9 +38,15 @@
     <t xml:space="preserve">Baza danych</t>
   </si>
   <si>
+    <t xml:space="preserve">3.5</t>
+  </si>
+  <si>
     <t xml:space="preserve">Prototypownie</t>
   </si>
   <si>
+    <t xml:space="preserve">5.5</t>
+  </si>
+  <si>
     <t xml:space="preserve">Prezentacja</t>
   </si>
   <si>
@@ -50,7 +56,13 @@
     <t xml:space="preserve">Pisanie testów</t>
   </si>
   <si>
+    <t xml:space="preserve">7.25</t>
+  </si>
+  <si>
     <t xml:space="preserve">Kopanie studni</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.5</t>
   </si>
   <si>
     <t xml:space="preserve">Pisanie kodu</t>
@@ -66,10 +78,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="3">
+  <numFmts count="4">
     <numFmt numFmtId="164" formatCode="General"/>
     <numFmt numFmtId="165" formatCode="yyyy/mm/dd;@"/>
     <numFmt numFmtId="166" formatCode="d/mm/yyyy"/>
+    <numFmt numFmtId="167" formatCode="@"/>
   </numFmts>
   <fonts count="6">
     <font>
@@ -151,7 +164,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -172,7 +185,11 @@
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="167" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -324,7 +341,7 @@
       <c r="B2" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="C2" s="1" t="n">
+      <c r="C2" s="5" t="n">
         <v>7</v>
       </c>
     </row>
@@ -335,8 +352,8 @@
       <c r="B3" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="C3" s="1" t="n">
-        <v>3.5</v>
+      <c r="C3" s="5" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -344,10 +361,10 @@
         <v>41075</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="C4" s="1" t="n">
-        <v>5.5</v>
+        <v>6</v>
+      </c>
+      <c r="C4" s="5" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -355,9 +372,9 @@
         <v>41076</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="C5" s="1" t="n">
+        <v>8</v>
+      </c>
+      <c r="C5" s="5" t="n">
         <v>3</v>
       </c>
     </row>
@@ -366,9 +383,9 @@
         <v>41078</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C6" s="1" t="n">
+        <v>9</v>
+      </c>
+      <c r="C6" s="5" t="n">
         <v>8</v>
       </c>
     </row>
@@ -418,10 +435,10 @@
         <v>41061</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C2" s="5" t="n">
-        <v>7.25</v>
+        <v>10</v>
+      </c>
+      <c r="C2" s="6" t="s">
+        <v>11</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -429,10 +446,10 @@
         <v>41062</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="C3" s="5" t="n">
-        <v>6.5</v>
+        <v>12</v>
+      </c>
+      <c r="C3" s="6" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -440,9 +457,9 @@
         <v>41063</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="C4" s="1" t="n">
+        <v>14</v>
+      </c>
+      <c r="C4" s="5" t="n">
         <v>4</v>
       </c>
     </row>
@@ -451,10 +468,10 @@
         <v>41067</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="C5" s="1" t="n">
-        <v>5.5</v>
+        <v>15</v>
+      </c>
+      <c r="C5" s="5" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -462,9 +479,9 @@
         <v>41068</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="C6" s="1" t="n">
+        <v>16</v>
+      </c>
+      <c r="C6" s="5" t="n">
         <v>2</v>
       </c>
     </row>
